--- a/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_sexo.xlsx
+++ b/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_sexo.xlsx
@@ -101,10 +101,10 @@
         <v>2001</v>
       </c>
       <c r="C2" s="1">
-        <v>0.48420247435569763</v>
+        <v>0.53309130668640137</v>
       </c>
       <c r="D2" s="1">
-        <v>48.420246124267578</v>
+        <v>53.309131622314453</v>
       </c>
     </row>
     <row r="3">
@@ -115,10 +115,10 @@
         <v>2001</v>
       </c>
       <c r="C3" s="1">
-        <v>0.42371562123298645</v>
+        <v>0.51956653594970703</v>
       </c>
       <c r="D3" s="1">
-        <v>42.371562957763672</v>
+        <v>51.956653594970703</v>
       </c>
     </row>
     <row r="4">
@@ -129,10 +129,10 @@
         <v>2003</v>
       </c>
       <c r="C4" s="1">
-        <v>0.46449622511863708</v>
+        <v>0.48458418250083923</v>
       </c>
       <c r="D4" s="1">
-        <v>46.449623107910156</v>
+        <v>48.458419799804688</v>
       </c>
     </row>
     <row r="5">
@@ -143,10 +143,10 @@
         <v>2003</v>
       </c>
       <c r="C5" s="1">
-        <v>0.39161249995231629</v>
+        <v>0.4497237503528595</v>
       </c>
       <c r="D5" s="1">
-        <v>39.161251068115234</v>
+        <v>44.972373962402344</v>
       </c>
     </row>
     <row r="6">
@@ -157,10 +157,10 @@
         <v>2005</v>
       </c>
       <c r="C6" s="1">
-        <v>0.34015741944313049</v>
+        <v>0.37322402000427246</v>
       </c>
       <c r="D6" s="1">
-        <v>34.015743255615234</v>
+        <v>37.322402954101563</v>
       </c>
     </row>
     <row r="7">
@@ -171,10 +171,10 @@
         <v>2005</v>
       </c>
       <c r="C7" s="1">
-        <v>0.27539998292922974</v>
+        <v>0.34831210970878601</v>
       </c>
       <c r="D7" s="1">
-        <v>27.539999008178711</v>
+        <v>34.831211090087891</v>
       </c>
     </row>
     <row r="8">
@@ -185,10 +185,10 @@
         <v>2007</v>
       </c>
       <c r="C8" s="1">
-        <v>0.28252705931663513</v>
+        <v>0.30666172504425049</v>
       </c>
       <c r="D8" s="1">
-        <v>28.252706527709961</v>
+        <v>30.666172027587891</v>
       </c>
     </row>
     <row r="9">
@@ -199,10 +199,10 @@
         <v>2007</v>
       </c>
       <c r="C9" s="1">
-        <v>0.21314384043216705</v>
+        <v>0.27914980053901672</v>
       </c>
       <c r="D9" s="1">
-        <v>21.314384460449219</v>
+        <v>27.914979934692383</v>
       </c>
     </row>
     <row r="10">
@@ -213,10 +213,10 @@
         <v>2008</v>
       </c>
       <c r="C10" s="1">
-        <v>0.262327641248703</v>
+        <v>0.2832341194152832</v>
       </c>
       <c r="D10" s="1">
-        <v>26.232763290405274</v>
+        <v>28.32341194152832</v>
       </c>
     </row>
     <row r="11">
@@ -227,10 +227,10 @@
         <v>2008</v>
       </c>
       <c r="C11" s="1">
-        <v>0.18809439241886139</v>
+        <v>0.25047355890274048</v>
       </c>
       <c r="D11" s="1">
-        <v>18.809438705444336</v>
+        <v>25.047355651855469</v>
       </c>
     </row>
     <row r="12">
@@ -241,10 +241,10 @@
         <v>2009</v>
       </c>
       <c r="C12" s="1">
-        <v>0.26215365529060364</v>
+        <v>0.29000231623649597</v>
       </c>
       <c r="D12" s="1">
-        <v>26.215366363525391</v>
+        <v>29.00023078918457</v>
       </c>
     </row>
     <row r="13">
@@ -255,10 +255,10 @@
         <v>2009</v>
       </c>
       <c r="C13" s="1">
-        <v>0.20738118886947632</v>
+        <v>0.2736031711101532</v>
       </c>
       <c r="D13" s="1">
-        <v>20.738119125366211</v>
+        <v>27.360317230224609</v>
       </c>
     </row>
     <row r="14">
@@ -269,10 +269,10 @@
         <v>2010</v>
       </c>
       <c r="C14" s="1">
-        <v>0.23302888870239258</v>
+        <v>0.25919586420059204</v>
       </c>
       <c r="D14" s="1">
-        <v>23.302888870239258</v>
+        <v>25.919586181640625</v>
       </c>
     </row>
     <row r="15">
@@ -283,10 +283,10 @@
         <v>2010</v>
       </c>
       <c r="C15" s="1">
-        <v>0.16791151463985443</v>
+        <v>0.23417453467845917</v>
       </c>
       <c r="D15" s="1">
-        <v>16.79115104675293</v>
+        <v>23.417453765869141</v>
       </c>
     </row>
     <row r="16">
@@ -297,10 +297,10 @@
         <v>2011</v>
       </c>
       <c r="C16" s="1">
-        <v>0.20236660540103912</v>
+        <v>0.2228815108537674</v>
       </c>
       <c r="D16" s="1">
-        <v>20.236660003662109</v>
+        <v>22.288150787353516</v>
       </c>
     </row>
     <row r="17">
@@ -311,10 +311,10 @@
         <v>2011</v>
       </c>
       <c r="C17" s="1">
-        <v>0.14852093160152435</v>
+        <v>0.19881486892700195</v>
       </c>
       <c r="D17" s="1">
-        <v>14.852092742919922</v>
+        <v>19.881486892700195</v>
       </c>
     </row>
     <row r="18">
@@ -325,10 +325,10 @@
         <v>2012</v>
       </c>
       <c r="C18" s="1">
-        <v>0.18296071887016296</v>
+        <v>0.20769469439983368</v>
       </c>
       <c r="D18" s="1">
-        <v>18.296072006225586</v>
+        <v>20.76947021484375</v>
       </c>
     </row>
     <row r="19">
@@ -339,10 +339,10 @@
         <v>2012</v>
       </c>
       <c r="C19" s="1">
-        <v>0.14022895693778992</v>
+        <v>0.20250622928142548</v>
       </c>
       <c r="D19" s="1">
-        <v>14.022895812988281</v>
+        <v>20.25062370300293</v>
       </c>
     </row>
     <row r="20">
@@ -353,10 +353,10 @@
         <v>2013</v>
       </c>
       <c r="C20" s="1">
-        <v>0.16949670016765594</v>
+        <v>0.18415924906730652</v>
       </c>
       <c r="D20" s="1">
-        <v>16.949670791625977</v>
+        <v>18.415924072265625</v>
       </c>
     </row>
     <row r="21">
@@ -367,10 +367,10 @@
         <v>2013</v>
       </c>
       <c r="C21" s="1">
-        <v>0.13136701285839081</v>
+        <v>0.17546689510345459</v>
       </c>
       <c r="D21" s="1">
-        <v>13.136701583862305</v>
+        <v>17.546689987182617</v>
       </c>
     </row>
     <row r="22">
@@ -381,10 +381,10 @@
         <v>2014</v>
       </c>
       <c r="C22" s="1">
-        <v>0.14947642385959625</v>
+        <v>0.16566622257232666</v>
       </c>
       <c r="D22" s="1">
-        <v>14.94764232635498</v>
+        <v>16.566621780395508</v>
       </c>
     </row>
     <row r="23">
@@ -395,10 +395,10 @@
         <v>2014</v>
       </c>
       <c r="C23" s="1">
-        <v>0.11235486716032028</v>
+        <v>0.15562102198600769</v>
       </c>
       <c r="D23" s="1">
-        <v>11.23548698425293</v>
+        <v>15.562102317810059</v>
       </c>
     </row>
     <row r="24">
@@ -409,10 +409,10 @@
         <v>2015</v>
       </c>
       <c r="C24" s="1">
-        <v>0.15560692548751831</v>
+        <v>0.17688997089862823</v>
       </c>
       <c r="D24" s="1">
-        <v>15.56069278717041</v>
+        <v>17.688997268676758</v>
       </c>
     </row>
     <row r="25">
@@ -423,10 +423,10 @@
         <v>2015</v>
       </c>
       <c r="C25" s="1">
-        <v>0.11161492764949799</v>
+        <v>0.16951444745063782</v>
       </c>
       <c r="D25" s="1">
-        <v>11.161492347717285</v>
+        <v>16.951444625854492</v>
       </c>
     </row>
     <row r="26">
@@ -437,10 +437,10 @@
         <v>2016</v>
       </c>
       <c r="C26" s="1">
-        <v>0.15765275061130524</v>
+        <v>0.18202805519104004</v>
       </c>
       <c r="D26" s="1">
-        <v>15.765275001525879</v>
+        <v>18.202804565429688</v>
       </c>
     </row>
     <row r="27">
@@ -451,10 +451,10 @@
         <v>2016</v>
       </c>
       <c r="C27" s="1">
-        <v>0.11909538507461548</v>
+        <v>0.17836311459541321</v>
       </c>
       <c r="D27" s="1">
-        <v>11.909538269042969</v>
+        <v>17.836311340332031</v>
       </c>
     </row>
     <row r="28">
@@ -465,10 +465,10 @@
         <v>2017</v>
       </c>
       <c r="C28" s="1">
-        <v>0.1418258398771286</v>
+        <v>0.16410580277442932</v>
       </c>
       <c r="D28" s="1">
-        <v>14.182583808898926</v>
+        <v>16.410579681396484</v>
       </c>
     </row>
     <row r="29">
@@ -479,10 +479,10 @@
         <v>2017</v>
       </c>
       <c r="C29" s="1">
-        <v>0.11100311577320099</v>
+        <v>0.17402076721191406</v>
       </c>
       <c r="D29" s="1">
-        <v>11.100311279296875</v>
+        <v>17.402076721191406</v>
       </c>
     </row>
     <row r="30">
@@ -493,10 +493,10 @@
         <v>2018</v>
       </c>
       <c r="C30" s="1">
-        <v>0.15806624293327332</v>
+        <v>0.22681738436222077</v>
       </c>
       <c r="D30" s="1">
-        <v>15.806624412536621</v>
+        <v>22.681737899780273</v>
       </c>
     </row>
     <row r="31">
@@ -507,10 +507,10 @@
         <v>2018</v>
       </c>
       <c r="C31" s="1">
-        <v>0.10942462086677551</v>
+        <v>0.23778663575649261</v>
       </c>
       <c r="D31" s="1">
-        <v>10.942461967468262</v>
+        <v>23.778663635253906</v>
       </c>
     </row>
     <row r="32">
@@ -521,10 +521,10 @@
         <v>2019</v>
       </c>
       <c r="C32" s="1">
-        <v>0.16870522499084473</v>
+        <v>0.1975235790014267</v>
       </c>
       <c r="D32" s="1">
-        <v>16.870521545410156</v>
+        <v>19.752357482910156</v>
       </c>
     </row>
     <row r="33">
@@ -535,10 +535,10 @@
         <v>2019</v>
       </c>
       <c r="C33" s="1">
-        <v>0.12192542105913162</v>
+        <v>0.20016022026538849</v>
       </c>
       <c r="D33" s="1">
-        <v>12.19254207611084</v>
+        <v>20.016021728515625</v>
       </c>
     </row>
     <row r="34">
@@ -549,10 +549,10 @@
         <v>2020</v>
       </c>
       <c r="C34" s="1">
-        <v>0.21688114106655121</v>
+        <v>0.25684836506843567</v>
       </c>
       <c r="D34" s="1">
-        <v>21.688114166259766</v>
+        <v>25.684837341308594</v>
       </c>
     </row>
     <row r="35">
@@ -563,10 +563,10 @@
         <v>2020</v>
       </c>
       <c r="C35" s="1">
-        <v>0.19351173937320709</v>
+        <v>0.26876005530357361</v>
       </c>
       <c r="D35" s="1">
-        <v>19.351173400878906</v>
+        <v>26.876005172729492</v>
       </c>
     </row>
     <row r="36">
@@ -577,10 +577,10 @@
         <v>2021</v>
       </c>
       <c r="C36" s="1">
-        <v>0.20066483318805695</v>
+        <v>0.22208166122436524</v>
       </c>
       <c r="D36" s="1">
-        <v>20.066482543945313</v>
+        <v>22.208166122436524</v>
       </c>
     </row>
     <row r="37">
@@ -591,10 +591,10 @@
         <v>2021</v>
       </c>
       <c r="C37" s="1">
-        <v>0.16534958779811859</v>
+        <v>0.2247653603553772</v>
       </c>
       <c r="D37" s="1">
-        <v>16.534957885742188</v>
+        <v>22.476535797119141</v>
       </c>
     </row>
     <row r="38">
@@ -605,10 +605,10 @@
         <v>2022</v>
       </c>
       <c r="C38" s="1">
-        <v>0.17537978291511536</v>
+        <v>0.1937033087015152</v>
       </c>
       <c r="D38" s="1">
-        <v>17.537979125976563</v>
+        <v>19.370330810546875</v>
       </c>
     </row>
     <row r="39">
@@ -619,10 +619,10 @@
         <v>2022</v>
       </c>
       <c r="C39" s="1">
-        <v>0.12964509427547455</v>
+        <v>0.19804410636425018</v>
       </c>
       <c r="D39" s="1">
-        <v>12.964509010314941</v>
+        <v>19.804410934448242</v>
       </c>
     </row>
     <row r="40">
@@ -633,10 +633,10 @@
         <v>2023</v>
       </c>
       <c r="C40" s="1">
-        <v>0.17463348805904388</v>
+        <v>0.19453082978725433</v>
       </c>
       <c r="D40" s="1">
-        <v>17.463348388671875</v>
+        <v>19.453083038330078</v>
       </c>
     </row>
     <row r="41">
@@ -647,10 +647,10 @@
         <v>2023</v>
       </c>
       <c r="C41" s="1">
-        <v>0.1378261148929596</v>
+        <v>0.20170783996582031</v>
       </c>
       <c r="D41" s="1">
-        <v>13.782611846923828</v>
+        <v>20.170783996582031</v>
       </c>
     </row>
     <row r="42">
@@ -661,10 +661,10 @@
         <v>2024</v>
       </c>
       <c r="C42" s="1">
-        <v>0.18807719647884369</v>
+        <v>0.21664059162139893</v>
       </c>
       <c r="D42" s="1">
-        <v>18.807720184326172</v>
+        <v>21.664058685302734</v>
       </c>
     </row>
     <row r="43">
@@ -675,10 +675,10 @@
         <v>2024</v>
       </c>
       <c r="C43" s="1">
-        <v>0.13528086245059967</v>
+        <v>0.20181079208850861</v>
       </c>
       <c r="D43" s="1">
-        <v>13.52808666229248</v>
+        <v>20.181079864501953</v>
       </c>
     </row>
     <row r="44">
@@ -689,10 +689,10 @@
         <v>2025</v>
       </c>
       <c r="C44" s="1">
-        <v>0.16185422241687775</v>
+        <v>0.17202626168727875</v>
       </c>
       <c r="D44" s="1">
-        <v>16.185422897338867</v>
+        <v>17.202625274658203</v>
       </c>
     </row>
     <row r="45">
@@ -703,10 +703,10 @@
         <v>2025</v>
       </c>
       <c r="C45" s="1">
-        <v>0.11079225689172745</v>
+        <v>0.1655876636505127</v>
       </c>
       <c r="D45" s="1">
-        <v>11.079225540161133</v>
+        <v>16.558765411376953</v>
       </c>
     </row>
   </sheetData>
